--- a/data/labour-market/Trends in sustained destinations following 16–18 study in the GWE/Medium-term change in sustained destinations, 201920 to 202223.xlsx
+++ b/data/labour-market/Trends in sustained destinations following 16–18 study in the GWE/Medium-term change in sustained destinations, 201920 to 202223.xlsx
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       <c r="AI25" s="2" t="inlineStr"/>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12454,7 @@
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12746,7 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
       <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13366,7 +13366,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       <c r="AI43" s="2" t="inlineStr"/>
       <c r="AJ43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13658,7 +13658,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
       <c r="AI44" s="2" t="inlineStr"/>
       <c r="AJ44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       <c r="AI45" s="2" t="inlineStr"/>
       <c r="AJ45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13950,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
       <c r="AI46" s="2" t="inlineStr"/>
       <c r="AJ46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       <c r="AI47" s="2" t="inlineStr"/>
       <c r="AJ47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14498,7 @@
       <c r="AI49" s="2" t="inlineStr"/>
       <c r="AJ49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
       <c r="AI50" s="2" t="inlineStr"/>
       <c r="AJ50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       <c r="AI51" s="2" t="inlineStr"/>
       <c r="AJ51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
       <c r="AI52" s="2" t="inlineStr"/>
       <c r="AJ52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       <c r="AI53" s="2" t="inlineStr"/>
       <c r="AJ53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15118,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15374,7 +15374,7 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
       <c r="AI56" s="2" t="inlineStr"/>
       <c r="AJ56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       <c r="AI57" s="2" t="inlineStr"/>
       <c r="AJ57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
       <c r="AI58" s="2" t="inlineStr"/>
       <c r="AJ58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15958,7 +15958,7 @@
       <c r="AI59" s="2" t="inlineStr"/>
       <c r="AJ59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
       <c r="AI60" s="2" t="inlineStr"/>
       <c r="AJ60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16250,7 +16250,7 @@
       <c r="AI61" s="2" t="inlineStr"/>
       <c r="AJ61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
       <c r="AI62" s="2" t="inlineStr"/>
       <c r="AJ62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       <c r="AI63" s="2" t="inlineStr"/>
       <c r="AJ63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
       <c r="AI64" s="2" t="inlineStr"/>
       <c r="AJ64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16818,7 +16818,7 @@
       <c r="AI65" s="2" t="inlineStr"/>
       <c r="AJ65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
       <c r="AI66" s="2" t="inlineStr"/>
       <c r="AJ66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       <c r="AI67" s="2" t="inlineStr"/>
       <c r="AJ67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
       <c r="AI68" s="2" t="inlineStr"/>
       <c r="AJ68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
       <c r="AI69" s="2" t="inlineStr"/>
       <c r="AJ69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17422,7 +17422,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
       <c r="AI70" s="2" t="inlineStr"/>
       <c r="AJ70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17678,7 +17678,7 @@
       <c r="AI71" s="2" t="inlineStr"/>
       <c r="AJ71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
       <c r="AI72" s="2" t="inlineStr"/>
       <c r="AJ72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17970,7 +17970,7 @@
       <c r="AI73" s="2" t="inlineStr"/>
       <c r="AJ73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18006,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
       <c r="AI74" s="2" t="inlineStr"/>
       <c r="AJ74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18262,7 +18262,7 @@
       <c r="AI75" s="2" t="inlineStr"/>
       <c r="AJ75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18298,7 +18298,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
       <c r="AI76" s="2" t="inlineStr"/>
       <c r="AJ76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18554,7 +18554,7 @@
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18846,7 @@
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18882,7 +18882,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19138,7 +19138,7 @@
       <c r="AI81" s="2" t="inlineStr"/>
       <c r="AJ81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
       <c r="AI82" s="2" t="inlineStr"/>
       <c r="AJ82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19430,7 @@
       <c r="AI83" s="2" t="inlineStr"/>
       <c r="AJ83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19466,7 +19466,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
       <c r="AI84" s="2" t="inlineStr"/>
       <c r="AJ84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19722,7 +19722,7 @@
       <c r="AI85" s="2" t="inlineStr"/>
       <c r="AJ85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20014,7 @@
       <c r="AI87" s="2" t="inlineStr"/>
       <c r="AJ87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20050,7 +20050,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
       <c r="AI88" s="2" t="inlineStr"/>
       <c r="AJ88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20306,7 @@
       <c r="AI89" s="2" t="inlineStr"/>
       <c r="AJ89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20342,7 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
       <c r="AI90" s="2" t="inlineStr"/>
       <c r="AJ90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20598,7 +20598,7 @@
       <c r="AI91" s="2" t="inlineStr"/>
       <c r="AJ91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20634,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
       <c r="AI92" s="2" t="inlineStr"/>
       <c r="AJ92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20890,7 +20890,7 @@
       <c r="AI93" s="2" t="inlineStr"/>
       <c r="AJ93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
       <c r="AI94" s="2" t="inlineStr"/>
       <c r="AJ94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       <c r="AI95" s="2" t="inlineStr"/>
       <c r="AJ95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21218,7 +21218,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
       <c r="AI96" s="2" t="inlineStr"/>
       <c r="AJ96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21458,7 +21458,7 @@
       <c r="AI97" s="2" t="inlineStr"/>
       <c r="AJ97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21584,7 +21584,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>21 July 2026</t>
+          <t>22 July 2026</t>
         </is>
       </c>
     </row>
